--- a/Xlsx/CreateCharacter.xlsx
+++ b/Xlsx/CreateCharacter.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Id</t>
   </si>
@@ -35,43 +35,10 @@
     <t>SceneID</t>
   </si>
   <si>
-    <t>GroupID</t>
-  </si>
-  <si>
-    <t>SceneName</t>
-  </si>
-  <si>
-    <t>SceneShowName</t>
-  </si>
-  <si>
-    <t>MaxGroup</t>
-  </si>
-  <si>
-    <t>MaxGroupPlayers</t>
-  </si>
-  <si>
-    <t>RelivePos</t>
-  </si>
-  <si>
-    <t>RelivePosEx</t>
-  </si>
-  <si>
-    <t>ResourcePos</t>
-  </si>
-  <si>
-    <t>Width</t>
-  </si>
-  <si>
-    <t>SoundList</t>
+    <t>Character</t>
   </si>
   <si>
     <t>Type</t>
-  </si>
-  <si>
-    <t>SubType</t>
-  </si>
-  <si>
-    <t>ActorID</t>
   </si>
   <si>
     <t>Int</t>
@@ -86,58 +53,16 @@
     <t>无需配置</t>
   </si>
   <si>
-    <t>最大组</t>
-  </si>
-  <si>
-    <t>每组最大人数</t>
-  </si>
-  <si>
-    <t>复活坐标列表</t>
-  </si>
-  <si>
-    <t>场景宽度</t>
-  </si>
-  <si>
-    <t>场景背景音乐列表</t>
-  </si>
-  <si>
-    <t>场景类型: 类型查看proto ESceneType</t>
-  </si>
-  <si>
-    <t>actorid</t>
+    <t>初始化角色</t>
   </si>
   <si>
     <t>SceneID_1</t>
   </si>
   <si>
-    <t>World</t>
-  </si>
-  <si>
-    <t>世界</t>
-  </si>
-  <si>
-    <t>0,0.5,0;1,0.5,1;2,0.5,3</t>
-  </si>
-  <si>
-    <t>10,10,10</t>
-  </si>
-  <si>
     <t>SceneID_2</t>
   </si>
   <si>
-    <t>Lobby</t>
-  </si>
-  <si>
-    <t>玩家个人大厅</t>
-  </si>
-  <si>
     <t>SceneID_3</t>
-  </si>
-  <si>
-    <t>PvpRoom</t>
-  </si>
-  <si>
-    <t>PVP对战房间</t>
   </si>
 </sst>
 </file>
@@ -774,7 +699,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -783,9 +708,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
@@ -1183,23 +1105,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="15.0916666666667" customWidth="1"/>
-    <col min="2" max="4" width="16.0916666666667" customWidth="1"/>
-    <col min="5" max="5" width="18.1833333333333" customWidth="1"/>
-    <col min="6" max="6" width="21.45" customWidth="1"/>
-    <col min="7" max="7" width="17.0916666666667" customWidth="1"/>
-    <col min="8" max="10" width="53.3666666666667" customWidth="1"/>
-    <col min="11" max="11" width="8.90833333333333" customWidth="1"/>
-    <col min="12" max="12" width="27.3666666666667" customWidth="1"/>
-    <col min="13" max="13" width="40.725" customWidth="1"/>
-    <col min="14" max="14" width="27.3666666666667" customWidth="1"/>
-    <col min="15" max="15" width="9.36666666666667" customWidth="1"/>
+    <col min="2" max="3" width="16.0916666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:15">
+    <row r="1" s="1" customFormat="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1209,389 +1122,115 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:3">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:3">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="B5" s="4">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:15">
-      <c r="A2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:15">
-      <c r="A3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="5">
+      <c r="B6" s="4">
         <v>0</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C6" s="4">
         <v>0</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4">
-        <v>99999</v>
-      </c>
-      <c r="G4">
-        <v>1000</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4">
-        <v>500</v>
-      </c>
-      <c r="L4" s="4"/>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="5">
-        <v>0</v>
-      </c>
-      <c r="C5" s="5">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5">
-        <v>9999999</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5">
-        <v>500</v>
-      </c>
-      <c r="L5" s="4"/>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="5">
-        <v>0</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6">
-        <v>99999</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6">
-        <v>500</v>
-      </c>
-      <c r="L6" s="4"/>
-      <c r="M6">
-        <v>2</v>
-      </c>
-      <c r="N6">
-        <v>2</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="L7" s="4"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="L8" s="4"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="L9" s="4"/>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="L10" s="4"/>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="L11" s="4"/>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="L12" s="4"/>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="L13" s="4"/>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="L14" s="4"/>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="L15" s="4"/>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="L16" s="4"/>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="L17" s="4"/>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="L18" s="4"/>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="L19" s="4"/>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="L20" s="4"/>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="L21" s="4"/>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="L22" s="4"/>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="L23" s="4"/>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="L24" s="4"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="3"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="3"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="3"/>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="3"/>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="3"/>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="3"/>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="3"/>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="3"/>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="3"/>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
